--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,20 +892,20 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
-      </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
         <v>0</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="D16" s="15">
         <v>3</v>
       </c>
+      <c r="E16" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I16" s="15">
         <v>6</v>
       </c>
       <c r="J16" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L16" s="14">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="M16" s="14">
-        <v>-79.310344827586</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.830508474576</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="I17" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J17" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K17" s="14">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="L17" s="14">
-        <v>-37.5</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M17" s="14">
-        <v>-16.666666666666</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N17" s="14">
-        <v>-66.666666666666</v>
+        <v>-67.567567567567</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
         <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18" s="14">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
         <v>5</v>
       </c>
       <c r="K18" s="14">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="L18" s="14">
-        <v>62.5</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M18" s="14">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N18" s="14">
-        <v>-87.962962962963</v>
+        <v>-88.372093023255</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F19" s="15">
         <v>30</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>-14.285714285714</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I19" s="15">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J19" s="15">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K19" s="14">
-        <v>-31.578947368421</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L19" s="14">
-        <v>-15.217391304347</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M19" s="14">
-        <v>-20.408163265306</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="N19" s="14">
-        <v>-35</v>
+        <v>-34.210526315789</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>4</v>
-      </c>
-      <c r="D20" s="15">
-        <v>4</v>
-      </c>
-      <c r="E20" s="14">
-        <v>0</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>22.222222222222</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="15">
         <v>14</v>
@@ -1128,10 +1128,10 @@
         <v>16.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.033994334277</v>
+        <v>-96.437659033078</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>9.433962264150</v>
       </c>
       <c r="I21" s="17">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J21" s="17">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.647058823529</v>
+        <v>-14.655172413793</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.222222222222</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="M21" s="18">
-        <v>-39.130434782608</v>
+        <v>-36.129032258064</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.407766990291</v>
+        <v>-86.269070735090</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="15">
         <v>1</v>
       </c>
       <c r="K23" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L23" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>-75</v>
+        <v>-62.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-41.379310344827</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="15">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G24" s="15">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H24" s="14">
-        <v>-7.627118644067</v>
+        <v>-11.711711711711</v>
       </c>
       <c r="I24" s="15">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="J24" s="15">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="K24" s="14">
-        <v>-4.605263157894</v>
+        <v>-7.386363636363</v>
       </c>
       <c r="L24" s="14">
-        <v>-2.027027027027</v>
+        <v>-11.413043478260</v>
       </c>
       <c r="M24" s="14">
-        <v>40.776699029126</v>
+        <v>41.739130434782</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="14">
-        <v>-11.111111111111</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="15">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G25" s="15">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H25" s="14">
-        <v>5.063291139240</v>
+        <v>-6.756756756756</v>
       </c>
       <c r="I25" s="15">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J25" s="15">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K25" s="14">
-        <v>8.823529411764</v>
+        <v>0</v>
       </c>
       <c r="L25" s="14">
-        <v>4.716981132075</v>
+        <v>-12.686567164179</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" s="14">
-        <v>31.25</v>
+        <v>58.823529411764</v>
       </c>
       <c r="I26" s="15">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J26" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K26" s="14">
-        <v>17.391304347826</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L26" s="14">
-        <v>-25</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="M26" s="14">
-        <v>-18.181818181818</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,20 +1384,20 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
-      </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="F16" s="15">
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-100</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L16" s="14">
-        <v>-76.923076923076</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="M16" s="14">
-        <v>-82.352941176470</v>
+        <v>-72.972972972973</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.307692307692</v>
+        <v>-89.130434782608</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>-12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I17" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J17" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" s="14">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L17" s="14">
-        <v>-45.454545454545</v>
+        <v>-44</v>
       </c>
       <c r="M17" s="14">
-        <v>-7.692307692307</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>-67.567567567567</v>
+        <v>-68.888888888888</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
         <v>1</v>
       </c>
       <c r="H18" s="14">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="I18" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="15">
         <v>5</v>
       </c>
       <c r="K18" s="14">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="L18" s="14">
-        <v>36.363636363636</v>
+        <v>45.454545454545</v>
       </c>
       <c r="M18" s="14">
-        <v>-44.444444444444</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N18" s="14">
-        <v>-88.372093023255</v>
+        <v>-89.189189189189</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="15">
         <v>30</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>3.448275862068</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I19" s="15">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J19" s="15">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K19" s="14">
-        <v>-24.242424242424</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.714285714285</v>
+        <v>-9.375</v>
       </c>
       <c r="M19" s="14">
-        <v>-13.793103448275</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="N19" s="14">
-        <v>-34.210526315789</v>
+        <v>-36.263736263736</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="14">
-        <v>-6.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="L20" s="14">
-        <v>16.666666666666</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M20" s="14">
-        <v>-36.363636363636</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.437659033078</v>
+        <v>-96.636771300448</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G21" s="17">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H21" s="18">
-        <v>9.433962264150</v>
+        <v>3.703703703703</v>
       </c>
       <c r="I21" s="17">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="J21" s="17">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.655172413793</v>
+        <v>-10.15625</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.255813953488</v>
+        <v>-19.580419580419</v>
       </c>
       <c r="M21" s="18">
-        <v>-36.129032258064</v>
+        <v>-36.464088397790</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.269070735090</v>
+        <v>-86.161251504211</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J23" s="15">
         <v>1</v>
       </c>
       <c r="K23" s="14">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M23" s="14">
-        <v>-62.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>-25</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="F24" s="15">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="G24" s="15">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H24" s="14">
-        <v>-11.711711711711</v>
+        <v>-25.471698113207</v>
       </c>
       <c r="I24" s="15">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="J24" s="15">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="K24" s="14">
-        <v>-7.386363636363</v>
+        <v>-11.055276381909</v>
       </c>
       <c r="L24" s="14">
-        <v>-11.413043478260</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="M24" s="14">
-        <v>41.739130434782</v>
+        <v>33.082706766917</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" s="14">
-        <v>-60</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G25" s="15">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H25" s="14">
-        <v>-6.756756756756</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I25" s="15">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J25" s="15">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K25" s="14">
-        <v>0</v>
+        <v>0.775193798449</v>
       </c>
       <c r="L25" s="14">
-        <v>-12.686567164179</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15">
         <v>27</v>
       </c>
       <c r="G26" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>58.823529411764</v>
+        <v>50</v>
       </c>
       <c r="I26" s="15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J26" s="15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K26" s="14">
-        <v>32.142857142857</v>
+        <v>31.25</v>
       </c>
       <c r="L26" s="14">
-        <v>-11.904761904761</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M26" s="14">
-        <v>-2.631578947368</v>
+        <v>2.439024390243</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,64 +892,64 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
+        <v>3</v>
+      </c>
+      <c r="J15" s="15">
+        <v>4</v>
+      </c>
+      <c r="K15" s="14">
+        <v>-25</v>
+      </c>
+      <c r="L15" s="14">
+        <v>50</v>
+      </c>
+      <c r="M15" s="14">
+        <v>50</v>
+      </c>
+      <c r="N15" s="14">
         <v>-50</v>
-      </c>
-      <c r="I15" s="15">
-        <v>2</v>
-      </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L15" s="14">
-        <v>0</v>
-      </c>
-      <c r="M15" s="14">
-        <v>100</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>4</v>
-      </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>100</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>-42.857142857142</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="15">
         <v>10</v>
@@ -961,13 +961,13 @@
         <v>-28.571428571428</v>
       </c>
       <c r="L16" s="14">
-        <v>-62.962962962963</v>
+        <v>-67.741935483871</v>
       </c>
       <c r="M16" s="14">
-        <v>-72.972972972973</v>
+        <v>-75</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.130434782608</v>
+        <v>-90.654205607476</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>-11.111111111111</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>-22.222222222222</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L17" s="14">
-        <v>-44</v>
+        <v>-28</v>
       </c>
       <c r="M17" s="14">
-        <v>-6.666666666666</v>
+        <v>20</v>
       </c>
       <c r="N17" s="14">
-        <v>-68.888888888888</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,7 +1016,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1034,22 +1034,22 @@
         <v>500</v>
       </c>
       <c r="I18" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15">
         <v>5</v>
       </c>
       <c r="K18" s="14">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="L18" s="14">
-        <v>45.454545454545</v>
+        <v>50</v>
       </c>
       <c r="M18" s="14">
-        <v>-46.666666666666</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="N18" s="14">
-        <v>-89.189189189189</v>
+        <v>-89.714285714285</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>33.333333333333</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F19" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G19" s="15">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>7.142857142857</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="I19" s="15">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J19" s="15">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="K19" s="14">
-        <v>-19.444444444444</v>
+        <v>-25.882352941176</v>
       </c>
       <c r="L19" s="14">
-        <v>-9.375</v>
+        <v>-16</v>
       </c>
       <c r="M19" s="14">
-        <v>-17.142857142857</v>
+        <v>-16</v>
       </c>
       <c r="N19" s="14">
-        <v>-36.263736263736</v>
+        <v>-40.566037735849</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K20" s="14">
-        <v>-6.25</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L20" s="14">
-        <v>7.142857142857</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M20" s="14">
-        <v>-46.428571428571</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.636771300448</v>
+        <v>-96.793587174348</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F21" s="17">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H21" s="18">
-        <v>3.703703703703</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I21" s="17">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="J21" s="17">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.15625</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.580419580419</v>
+        <v>-21.472392638036</v>
       </c>
       <c r="M21" s="18">
-        <v>-36.464088397790</v>
+        <v>-35.353535353535</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.161251504211</v>
+        <v>-86.526315789473</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>3</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1248,7 +1248,7 @@
         <v>500</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M23" s="14">
         <v>-33.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>-39.130434782608</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G24" s="15">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H24" s="14">
-        <v>-25.471698113207</v>
+        <v>-28.723404255319</v>
       </c>
       <c r="I24" s="15">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="J24" s="15">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="K24" s="14">
-        <v>-11.055276381909</v>
+        <v>-10.138248847926</v>
       </c>
       <c r="L24" s="14">
-        <v>-18.055555555555</v>
+        <v>-19.087136929460</v>
       </c>
       <c r="M24" s="14">
-        <v>33.082706766917</v>
+        <v>28.289473684210</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>8.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F25" s="15">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G25" s="15">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H25" s="14">
-        <v>-4.761904761904</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I25" s="15">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J25" s="15">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K25" s="14">
-        <v>0.775193798449</v>
+        <v>2.173913043478</v>
       </c>
       <c r="L25" s="14">
-        <v>-16.666666666666</v>
+        <v>-22.527472527472</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>25</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H26" s="14">
         <v>50</v>
       </c>
       <c r="I26" s="15">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J26" s="15">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K26" s="14">
-        <v>31.25</v>
+        <v>22.5</v>
       </c>
       <c r="L26" s="14">
-        <v>-4.545454545454</v>
+        <v>-5.769230769230</v>
       </c>
       <c r="M26" s="14">
-        <v>2.439024390243</v>
+        <v>6.521739130434</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1437,11 +1437,11 @@
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-100</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="15">
         <v>1</v>
@@ -1453,7 +1453,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="15">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>-100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -884,7 +884,7 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -892,40 +892,40 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="H15" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I15" s="14">
         <v>3</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>4</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
         <v>-25</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="15">
         <v>50</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>50</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>-50</v>
       </c>
     </row>
@@ -933,8 +933,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -942,196 +942,196 @@
       <c r="E16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="15">
-        <v>4</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
         <v>5</v>
       </c>
-      <c r="H16" s="14">
-        <v>-20</v>
-      </c>
-      <c r="I16" s="15">
-        <v>10</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="H16" s="15">
+        <v>20</v>
+      </c>
+      <c r="I16" s="14">
+        <v>12</v>
+      </c>
+      <c r="J16" s="14">
         <v>14</v>
       </c>
-      <c r="K16" s="14">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-67.741935483871</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-75</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-90.654205607476</v>
+      <c r="K16" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-70.731707317073</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-89.830508474576</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>4</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="14">
         <v>1</v>
       </c>
-      <c r="E17" s="14">
-        <v>300</v>
-      </c>
-      <c r="F17" s="15">
-        <v>11</v>
-      </c>
-      <c r="G17" s="15">
+      <c r="D17" s="14">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>10</v>
+      </c>
+      <c r="G17" s="14">
         <v>6</v>
       </c>
-      <c r="H17" s="14">
-        <v>83.333333333333</v>
-      </c>
-      <c r="I17" s="15">
-        <v>18</v>
-      </c>
-      <c r="J17" s="15">
-        <v>19</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-5.263157894736</v>
-      </c>
-      <c r="L17" s="14">
-        <v>-28</v>
-      </c>
-      <c r="M17" s="14">
-        <v>20</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-64</v>
+      <c r="H17" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="I17" s="14">
+        <v>20</v>
+      </c>
+      <c r="J17" s="14">
+        <v>20</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="M17" s="15">
+        <v>25</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-62.962962962963</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
         <v>6</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <v>1</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="15">
         <v>500</v>
       </c>
-      <c r="I18" s="15">
-        <v>18</v>
-      </c>
-      <c r="J18" s="15">
-        <v>5</v>
-      </c>
-      <c r="K18" s="14">
-        <v>260</v>
-      </c>
-      <c r="L18" s="14">
-        <v>50</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-48.571428571428</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-89.714285714285</v>
+      <c r="I18" s="14">
+        <v>20</v>
+      </c>
+      <c r="J18" s="14">
+        <v>6</v>
+      </c>
+      <c r="K18" s="15">
+        <v>233.333333333333</v>
+      </c>
+      <c r="L18" s="15">
+        <v>53.846153846153</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-53.488372093023</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-89.743589743589</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>5</v>
-      </c>
-      <c r="D19" s="15">
-        <v>13</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-61.538461538461</v>
-      </c>
-      <c r="F19" s="15">
-        <v>31</v>
-      </c>
-      <c r="G19" s="15">
-        <v>35</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-11.428571428571</v>
-      </c>
-      <c r="I19" s="15">
-        <v>63</v>
-      </c>
-      <c r="J19" s="15">
-        <v>85</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-25.882352941176</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-16</v>
-      </c>
-      <c r="M19" s="14">
-        <v>-16</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-40.566037735849</v>
+      <c r="C19" s="14">
+        <v>12</v>
+      </c>
+      <c r="D19" s="14">
+        <v>11</v>
+      </c>
+      <c r="E19" s="15">
+        <v>9.090909090909</v>
+      </c>
+      <c r="F19" s="14">
+        <v>36</v>
+      </c>
+      <c r="G19" s="14">
+        <v>39</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-7.692307692307</v>
+      </c>
+      <c r="I19" s="14">
+        <v>76</v>
+      </c>
+      <c r="J19" s="14">
+        <v>96</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-20.833333333333</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-16.483516483516</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-10.588235294117</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-39.2</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="F20" s="15">
-        <v>6</v>
-      </c>
-      <c r="G20" s="15">
-        <v>8</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-25</v>
-      </c>
-      <c r="I20" s="15">
+      <c r="I20" s="14">
         <v>16</v>
       </c>
-      <c r="J20" s="15">
-        <v>19</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-15.789473684210</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-11.111111111111</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-48.387096774193</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-96.793587174348</v>
+      <c r="J20" s="14">
+        <v>21</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-23.809523809523</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-40.740740740740</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-97.168141592920</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.777777777777</v>
+        <v>6.25</v>
       </c>
       <c r="F21" s="17">
+        <v>61</v>
+      </c>
+      <c r="G21" s="17">
         <v>60</v>
       </c>
-      <c r="G21" s="17">
-        <v>57</v>
-      </c>
       <c r="H21" s="18">
-        <v>5.263157894736</v>
+        <v>1.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="J21" s="17">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.328767123287</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.472392638036</v>
+        <v>-23.036649214659</v>
       </c>
       <c r="M21" s="18">
-        <v>-35.353535353535</v>
+        <v>-34.080717488789</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.526315789473</v>
+        <v>-86.261682242990</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1229,7 +1229,7 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="14">
         <v>5</v>
       </c>
       <c r="G23" s="13" t="s">
@@ -1238,20 +1238,20 @@
       <c r="H23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="15">
-        <v>6</v>
-      </c>
-      <c r="J23" s="15">
+      <c r="I23" s="14">
+        <v>7</v>
+      </c>
+      <c r="J23" s="14">
         <v>1</v>
       </c>
-      <c r="K23" s="14">
-        <v>500</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="M23" s="14">
-        <v>-33.333333333333</v>
+      <c r="K23" s="15">
+        <v>600</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
+        <v>-22.222222222222</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>18</v>
-      </c>
-      <c r="D24" s="15">
-        <v>18</v>
-      </c>
-      <c r="E24" s="14">
-        <v>0</v>
-      </c>
-      <c r="F24" s="15">
-        <v>67</v>
-      </c>
-      <c r="G24" s="15">
-        <v>94</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-28.723404255319</v>
-      </c>
-      <c r="I24" s="15">
-        <v>195</v>
-      </c>
-      <c r="J24" s="15">
-        <v>217</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-10.138248847926</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-19.087136929460</v>
-      </c>
-      <c r="M24" s="14">
-        <v>28.289473684210</v>
+      <c r="C24" s="14">
+        <v>24</v>
+      </c>
+      <c r="D24" s="14">
+        <v>13</v>
+      </c>
+      <c r="E24" s="15">
+        <v>84.615384615384</v>
+      </c>
+      <c r="F24" s="14">
+        <v>74</v>
+      </c>
+      <c r="G24" s="14">
+        <v>78</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-5.128205128205</v>
+      </c>
+      <c r="I24" s="14">
+        <v>218</v>
+      </c>
+      <c r="J24" s="14">
+        <v>230</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-5.217391304347</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-16.793893129771</v>
+      </c>
+      <c r="M24" s="15">
+        <v>33.742331288343</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>11</v>
-      </c>
-      <c r="D25" s="15">
-        <v>9</v>
-      </c>
-      <c r="E25" s="14">
-        <v>22.222222222222</v>
-      </c>
-      <c r="F25" s="15">
-        <v>46</v>
-      </c>
-      <c r="G25" s="15">
-        <v>54</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-14.814814814814</v>
-      </c>
-      <c r="I25" s="15">
-        <v>141</v>
-      </c>
-      <c r="J25" s="15">
-        <v>138</v>
-      </c>
-      <c r="K25" s="14">
-        <v>2.173913043478</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-22.527472527472</v>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>12</v>
+      </c>
+      <c r="E25" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="F25" s="14">
+        <v>50</v>
+      </c>
+      <c r="G25" s="14">
+        <v>48</v>
+      </c>
+      <c r="H25" s="15">
+        <v>4.166666666666</v>
+      </c>
+      <c r="I25" s="14">
+        <v>161</v>
+      </c>
+      <c r="J25" s="14">
+        <v>150</v>
+      </c>
+      <c r="K25" s="15">
+        <v>7.333333333333</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-21.463414634146</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>7</v>
-      </c>
-      <c r="D26" s="15">
-        <v>8</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-12.5</v>
-      </c>
-      <c r="F26" s="15">
-        <v>30</v>
-      </c>
-      <c r="G26" s="15">
-        <v>20</v>
-      </c>
-      <c r="H26" s="14">
-        <v>50</v>
-      </c>
-      <c r="I26" s="15">
-        <v>49</v>
-      </c>
-      <c r="J26" s="15">
-        <v>40</v>
-      </c>
-      <c r="K26" s="14">
-        <v>22.5</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-5.769230769230</v>
-      </c>
-      <c r="M26" s="14">
-        <v>6.521739130434</v>
+      <c r="C26" s="14">
+        <v>4</v>
+      </c>
+      <c r="D26" s="14">
+        <v>4</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>25</v>
+      </c>
+      <c r="G26" s="14">
+        <v>21</v>
+      </c>
+      <c r="H26" s="15">
+        <v>19.047619047619</v>
+      </c>
+      <c r="I26" s="14">
+        <v>52</v>
+      </c>
+      <c r="J26" s="14">
+        <v>44</v>
+      </c>
+      <c r="K26" s="15">
+        <v>18.181818181818</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-8.771929824561</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,34 +1384,34 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="H27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>4</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="15">
         <v>-25</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="15">
         <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="15">
+      <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="J28" s="15">
-        <v>3</v>
-      </c>
-      <c r="K28" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-66.666666666666</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>1</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I28" s="14">
+        <v>2</v>
+      </c>
+      <c r="J28" s="14">
+        <v>5</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,37 +1469,37 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="15">
-        <v>1</v>
-      </c>
-      <c r="K29" s="14">
+      <c r="J29" s="14">
+        <v>2</v>
+      </c>
+      <c r="K29" s="15">
         <v>-100</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="15">
         <v>-100</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-100</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1510,37 +1510,37 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="15">
-        <v>1</v>
-      </c>
-      <c r="K30" s="14">
+      <c r="J30" s="14">
+        <v>2</v>
+      </c>
+      <c r="K30" s="15">
         <v>-100</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
         <v>-100</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-100</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1548,34 +1548,34 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="15">
-        <v>1</v>
-      </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="15">
         <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>13</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>14</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>4</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>3</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>5</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>66.666666666666</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>25</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-64.285714285714</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-61.538461538461</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>15</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>24</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>25</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>17</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>14</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>-17.647058823529</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-44</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-41.666666666666</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-6.666666666666</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>775</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>708</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>413</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>265</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>109</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-58.867924528301</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-73.607748184019</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-84.604519774011</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-85.935483870967</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>249</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>314</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>208</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>161</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>161</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>0</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-22.596153846153</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-48.726114649681</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-35.341365461847</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1119</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1165</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>537</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>339</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>67</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-80.23598820059</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-87.523277467411</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-94.248927038626</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-94.012511170688</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>988</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>653</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>566</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>536</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>511</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-4.664179104477</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-9.717314487632</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-21.745788667687</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-48.279352226720</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>3116</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>2730</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>845</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>497</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>155</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-68.812877263581</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-81.656804733727</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-94.322344322344</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-95.025673940949</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
         <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-62.5</v>
+        <v>-57.575757575757</v>
       </c>
       <c r="M16" s="15">
-        <v>-70.731707317073</v>
+        <v>-67.441860465116</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.830508474576</v>
+        <v>-89.230769230769</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
-      </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H17" s="15">
-        <v>66.666666666666</v>
+        <v>175</v>
       </c>
       <c r="I17" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J17" s="14">
         <v>20</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.076923076923</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N17" s="15">
-        <v>-62.962962962963</v>
+        <v>-59.322033898305</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
         <v>20</v>
       </c>
       <c r="J18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K18" s="15">
-        <v>233.333333333333</v>
+        <v>122.222222222222</v>
       </c>
       <c r="L18" s="15">
         <v>53.846153846153</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.488372093023</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.743589743589</v>
+        <v>-90.697674418604</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
         <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.692307692307</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="I19" s="14">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J19" s="14">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.833333333333</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.483516483516</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-10.588235294117</v>
+        <v>-12.371134020618</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.2</v>
+        <v>-35.606060606060</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>-23.809523809523</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.740740740740</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-55.555555555555</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.168141592920</v>
+        <v>-97.157190635451</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>6.25</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F21" s="17">
+        <v>63</v>
+      </c>
+      <c r="G21" s="17">
         <v>61</v>
       </c>
-      <c r="G21" s="17">
-        <v>60</v>
-      </c>
       <c r="H21" s="18">
-        <v>1.666666666666</v>
+        <v>3.278688524590</v>
       </c>
       <c r="I21" s="17">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="J21" s="17">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.259259259259</v>
+        <v>-7.344632768361</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.036649214659</v>
+        <v>-21.531100478468</v>
       </c>
       <c r="M21" s="18">
-        <v>-34.080717488789</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.261682242990</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
         <v>1</v>
       </c>
       <c r="K23" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>84.615384615384</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.128205128205</v>
+        <v>2.531645569620</v>
       </c>
       <c r="I24" s="14">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="J24" s="14">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.217391304347</v>
+        <v>-4.705882352941</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.793893129771</v>
+        <v>-18.456375838926</v>
       </c>
       <c r="M24" s="15">
-        <v>33.742331288343</v>
+        <v>35.754189944134</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>6.25</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G25" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>4.166666666666</v>
+        <v>24.489795918367</v>
       </c>
       <c r="I25" s="14">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J25" s="14">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K25" s="15">
-        <v>7.333333333333</v>
+        <v>7.228915662650</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.463414634146</v>
+        <v>-24.255319148936</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>19.047619047619</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I26" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J26" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K26" s="15">
-        <v>18.181818181818</v>
+        <v>12</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.771929824561</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>5.660377358490</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I28" s="14">
+        <v>3</v>
+      </c>
+      <c r="J28" s="14">
+        <v>6</v>
+      </c>
+      <c r="K28" s="15">
         <v>-50</v>
       </c>
-      <c r="F28" s="14">
-        <v>1</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-50</v>
-      </c>
-      <c r="I28" s="14">
-        <v>2</v>
-      </c>
-      <c r="J28" s="14">
-        <v>5</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-60</v>
-      </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
-      </c>
-      <c r="G16" s="14">
-        <v>2</v>
-      </c>
-      <c r="H16" s="15">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
         <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-57.575757575757</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M16" s="15">
-        <v>-67.441860465116</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.230769230769</v>
+        <v>-88.489208633093</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -977,79 +977,79 @@
       <c r="C17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="15">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K17" s="15">
-        <v>20</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.285714285714</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="M17" s="15">
-        <v>41.176470588235</v>
+        <v>30</v>
       </c>
       <c r="N17" s="15">
-        <v>-59.322033898305</v>
+        <v>-61.764705882352</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K18" s="15">
-        <v>122.222222222222</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L18" s="15">
-        <v>53.846153846153</v>
+        <v>73.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.333333333333</v>
+        <v>-52.727272727272</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.697674418604</v>
+        <v>-88.793103448275</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
         <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.820512820512</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="I19" s="14">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.047619047619</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="M19" s="15">
-        <v>-12.371134020618</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="N19" s="15">
-        <v>-35.606060606060</v>
+        <v>-32.867132867132</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>-29.166666666666</v>
+        <v>-24</v>
       </c>
       <c r="L20" s="15">
-        <v>-43.333333333333</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.536585365853</v>
+        <v>-57.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.157190635451</v>
+        <v>-97.035881435257</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>25</v>
+      </c>
+      <c r="D21" s="17">
         <v>16</v>
       </c>
-      <c r="D21" s="17">
-        <v>15</v>
-      </c>
       <c r="E21" s="18">
-        <v>6.666666666666</v>
+        <v>56.25</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>3.278688524590</v>
+        <v>9.230769230769</v>
       </c>
       <c r="I21" s="17">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="J21" s="17">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.344632768361</v>
+        <v>-2.590673575129</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.531100478468</v>
+        <v>-19.658119658119</v>
       </c>
       <c r="M21" s="18">
-        <v>-33.870967741935</v>
+        <v>-31.884057971014</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.714285714285</v>
+        <v>-84.801940177849</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1248,10 +1248,10 @@
         <v>700</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>19.047619047619</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>2.531645569620</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I24" s="14">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="J24" s="14">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.705882352941</v>
+        <v>-3.260869565217</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.456375838926</v>
+        <v>-21.700879765395</v>
       </c>
       <c r="M24" s="15">
-        <v>35.754189944134</v>
+        <v>36.224489795918</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>6.25</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F25" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>24.489795918367</v>
+        <v>26.785714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="J25" s="14">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="K25" s="15">
-        <v>7.228915662650</v>
+        <v>9.189189189189</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.255319148936</v>
+        <v>-25.461254612546</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.090909090909</v>
+        <v>8</v>
       </c>
       <c r="I26" s="14">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J26" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K26" s="15">
-        <v>12</v>
+        <v>19.298245614035</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.677419354838</v>
+        <v>-1.449275362318</v>
       </c>
       <c r="M26" s="15">
-        <v>5.660377358490</v>
+        <v>13.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,29 +1428,29 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
         <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="15">
+        <v>28.571428571428</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>14.285714285714</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L16" s="15">
-        <v>-52.941176470588</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="M16" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.461538461538</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.489208633093</v>
+        <v>-87.898089171974</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>120</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J17" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K17" s="15">
-        <v>13.043478260869</v>
+        <v>32</v>
       </c>
       <c r="L17" s="15">
-        <v>-10.344827586206</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="M17" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.764705882352</v>
+        <v>-54.166666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>5</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>42.857142857142</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="14">
         <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="15">
-        <v>116.666666666667</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L18" s="15">
         <v>73.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.727272727272</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.793103448275</v>
+        <v>-89.803921568627</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
         <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.904761904761</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="J19" s="14">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.789473684210</v>
+        <v>-15.447154471544</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.311475409836</v>
+        <v>-26.760563380281</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.433962264150</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N19" s="15">
-        <v>-32.867132867132</v>
+        <v>-36.196319018404</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,22 +1098,22 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>19</v>
@@ -1128,10 +1128,10 @@
         <v>-38.709677419354</v>
       </c>
       <c r="M20" s="15">
-        <v>-57.777777777777</v>
+        <v>-61.224489795918</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.035881435257</v>
+        <v>-97.308781869688</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>56.25</v>
+        <v>-5</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>9.230769230769</v>
+        <v>13.432835820895</v>
       </c>
       <c r="I21" s="17">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="J21" s="17">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.590673575129</v>
+        <v>-3.286384976525</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.658119658119</v>
+        <v>-20.463320463320</v>
       </c>
       <c r="M21" s="18">
-        <v>-31.884057971014</v>
+        <v>-32.459016393442</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.801940177849</v>
+        <v>-84.930504754937</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1251,7 +1251,7 @@
         <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>19.047619047619</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="J24" s="14">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.260869565217</v>
+        <v>-7.817589576547</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.700879765395</v>
+        <v>-25.132275132275</v>
       </c>
       <c r="M24" s="15">
-        <v>36.224489795918</v>
+        <v>31.627906976744</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>21.052631578947</v>
+        <v>-31.25</v>
       </c>
       <c r="F25" s="14">
         <v>71</v>
       </c>
       <c r="G25" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H25" s="15">
-        <v>26.785714285714</v>
+        <v>12.698412698412</v>
       </c>
       <c r="I25" s="14">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J25" s="14">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="K25" s="15">
-        <v>9.189189189189</v>
+        <v>5.970149253731</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.461254612546</v>
+        <v>-31.067961165048</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J26" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K26" s="15">
-        <v>19.298245614035</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.449275362318</v>
+        <v>-4.109589041095</v>
       </c>
       <c r="M26" s="15">
-        <v>13.333333333333</v>
+        <v>4.477611940298</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,23 +1396,23 @@
       <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
+        <v>8</v>
+      </c>
+      <c r="G16" s="14">
         <v>9</v>
       </c>
-      <c r="G16" s="14">
-        <v>7</v>
-      </c>
       <c r="H16" s="15">
-        <v>28.571428571428</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.523809523809</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.117647058823</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.461538461538</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.898089171974</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
         <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
         <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I17" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J17" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" s="15">
-        <v>32</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.941176470588</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="M17" s="15">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.166666666666</v>
+        <v>-51.351351351351</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-11.111111111111</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>85.714285714285</v>
+        <v>80</v>
       </c>
       <c r="L18" s="15">
-        <v>73.333333333333</v>
+        <v>58.823529411764</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.666666666666</v>
+        <v>-55.737704918032</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.803921568627</v>
+        <v>-90.287769784172</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
         <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>5.263157894736</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J19" s="14">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.447154471544</v>
+        <v>-14.393939393939</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.760563380281</v>
+        <v>-26.143790849673</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.111111111111</v>
+        <v>-6.611570247933</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.196319018404</v>
+        <v>-39.247311827957</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>4</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
         <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>-24</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.709677419354</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="M20" s="15">
-        <v>-61.224489795918</v>
+        <v>-62.264150943396</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.308781869688</v>
+        <v>-97.329773030707</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-5</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>13.432835820895</v>
+        <v>10.294117647058</v>
       </c>
       <c r="I21" s="17">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="J21" s="17">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.286384976525</v>
+        <v>-3.478260869565</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.463320463320</v>
+        <v>-20.143884892086</v>
       </c>
       <c r="M21" s="18">
-        <v>-32.459016393442</v>
+        <v>-31.692307692307</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.930504754937</v>
+        <v>-84.908225696804</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,35 +1223,35 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="15">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="L23" s="15">
         <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>-27.272727272727</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-48.387096774193</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-2.970297029702</v>
       </c>
       <c r="I24" s="14">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="J24" s="14">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.817589576547</v>
+        <v>-4.833836858006</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.132275132275</v>
+        <v>-23.357664233576</v>
       </c>
       <c r="M24" s="15">
-        <v>31.627906976744</v>
+        <v>35.775862068965</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-31.25</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F25" s="14">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G25" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H25" s="15">
-        <v>12.698412698412</v>
+        <v>-10</v>
       </c>
       <c r="I25" s="14">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="J25" s="14">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="K25" s="15">
-        <v>5.970149253731</v>
+        <v>2.272727272727</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.067961165048</v>
+        <v>-33.628318584070</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-60</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
         <v>22</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J26" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K26" s="15">
-        <v>12.903225806451</v>
+        <v>10.294117647058</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.109589041095</v>
+        <v>-1.315789473684</v>
       </c>
       <c r="M26" s="15">
-        <v>4.477611940298</v>
+        <v>5.633802816901</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
@@ -1453,7 +1453,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
         <v>100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-11.111111111111</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.043478260869</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.857142857142</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="M16" s="15">
-        <v>-66.666666666666</v>
+        <v>-59.016393442622</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.235294117647</v>
+        <v>-85.875706214689</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>16</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H17" s="15">
-        <v>166.666666666667</v>
+        <v>77.777777777777</v>
       </c>
       <c r="I17" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K17" s="15">
-        <v>38.461538461538</v>
+        <v>37.931034482758</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.702702702702</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M17" s="15">
-        <v>44</v>
+        <v>48.148148148148</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.351351351351</v>
+        <v>-47.368421052631</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>80</v>
+        <v>82.352941176470</v>
       </c>
       <c r="L18" s="15">
-        <v>58.823529411764</v>
+        <v>82.352941176470</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.737704918032</v>
+        <v>-53.731343283582</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.287769784172</v>
+        <v>-90.342679127725</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F19" s="14">
+        <v>36</v>
+      </c>
+      <c r="G19" s="14">
         <v>38</v>
       </c>
-      <c r="G19" s="14">
-        <v>36</v>
-      </c>
       <c r="H19" s="15">
-        <v>5.555555555555</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J19" s="14">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.393939393939</v>
+        <v>-16.083916083916</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.143790849673</v>
+        <v>-26.380368098159</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.611570247933</v>
+        <v>-6.25</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.247311827957</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
         <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.034482758620</v>
+        <v>-18.75</v>
       </c>
       <c r="L20" s="15">
-        <v>-39.393939393939</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M20" s="15">
-        <v>-62.264150943396</v>
+        <v>-51.851851851851</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.329773030707</v>
+        <v>-96.758104738154</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.882352941176</v>
+        <v>-4</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>10.294117647058</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I21" s="17">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="J21" s="17">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.478260869565</v>
+        <v>-2.745098039215</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.143884892086</v>
+        <v>-16.498316498316</v>
       </c>
       <c r="M21" s="18">
-        <v>-31.692307692307</v>
+        <v>-27.485380116959</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.908225696804</v>
+        <v>-84.402515723270</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I23" s="14">
+        <v>10</v>
+      </c>
+      <c r="J23" s="14">
+        <v>4</v>
+      </c>
+      <c r="K23" s="15">
+        <v>150</v>
+      </c>
+      <c r="L23" s="15">
         <v>0</v>
       </c>
-      <c r="I23" s="14">
-        <v>8</v>
-      </c>
-      <c r="J23" s="14">
-        <v>2</v>
-      </c>
-      <c r="K23" s="15">
-        <v>300</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-20</v>
-      </c>
       <c r="M23" s="15">
-        <v>-38.461538461538</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.970297029702</v>
+        <v>-12.745098039215</v>
       </c>
       <c r="I24" s="14">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="J24" s="14">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.833836858006</v>
+        <v>-7.282913165266</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.357664233576</v>
+        <v>-24.601366742596</v>
       </c>
       <c r="M24" s="15">
-        <v>35.775862068965</v>
+        <v>31.349206349206</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.842105263157</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="F25" s="14">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H25" s="15">
-        <v>-10</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="J25" s="14">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="K25" s="15">
-        <v>2.272727272727</v>
+        <v>-2.489626556016</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.628318584070</v>
+        <v>-35.616438356164</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="F26" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.333333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I26" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K26" s="15">
-        <v>10.294117647058</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.315789473684</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="M26" s="15">
-        <v>5.633802816901</v>
+        <v>-8.433734939759</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>200</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="L27" s="15">
         <v>133.333333333333</v>
@@ -1435,10 +1435,10 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.428571428571</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I16" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.714285714285</v>
+        <v>-9.375</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.476190476190</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="M16" s="15">
-        <v>-59.016393442622</v>
+        <v>-56.060606060606</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.875706214689</v>
+        <v>-84.816753926701</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,13 +975,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>16</v>
@@ -993,63 +993,63 @@
         <v>77.777777777777</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K17" s="15">
-        <v>37.931034482758</v>
+        <v>37.5</v>
       </c>
       <c r="L17" s="15">
-        <v>5.263157894736</v>
+        <v>10</v>
       </c>
       <c r="M17" s="15">
-        <v>48.148148148148</v>
+        <v>46.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.368421052631</v>
+        <v>-46.987951807228</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>82.352941176470</v>
+        <v>72.222222222222</v>
       </c>
       <c r="L18" s="15">
         <v>82.352941176470</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.731343283582</v>
+        <v>-60.256410256410</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.342679127725</v>
+        <v>-91.091954022988</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
         <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.263157894736</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="I19" s="14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J19" s="14">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.083916083916</v>
+        <v>-14.473684210526</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.380368098159</v>
+        <v>-26.136363636363</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.25</v>
+        <v>-6.474820143884</v>
       </c>
       <c r="N19" s="15">
-        <v>-40</v>
+        <v>-38.095238095238</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
         <v>100</v>
       </c>
       <c r="F20" s="14">
+        <v>12</v>
+      </c>
+      <c r="G20" s="14">
         <v>9</v>
       </c>
-      <c r="G20" s="14">
-        <v>8</v>
-      </c>
       <c r="H20" s="15">
-        <v>12.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.75</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.529411764705</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="M20" s="15">
-        <v>-51.851851851851</v>
+        <v>-44.642857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.758104738154</v>
+        <v>-96.370023419203</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-4</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="J21" s="17">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.745098039215</v>
+        <v>-1.094890510948</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.498316498316</v>
+        <v>-15.576323987538</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.485380116959</v>
+        <v>-27.540106951871</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.402515723270</v>
+        <v>-84.058823529411</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-50</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
         <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>-23.076923076923</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-46.153846153846</v>
+        <v>12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.745098039215</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="J24" s="14">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.282913165266</v>
+        <v>-6.299212598425</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.601366742596</v>
+        <v>-23.554603854389</v>
       </c>
       <c r="M24" s="15">
-        <v>31.349206349206</v>
+        <v>33.208955223880</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>-61.904761904761</v>
+        <v>-15</v>
       </c>
       <c r="F25" s="14">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G25" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="15">
-        <v>-25.333333333333</v>
+        <v>-35.526315789473</v>
       </c>
       <c r="I25" s="14">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="J25" s="14">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.489626556016</v>
+        <v>-3.831417624521</v>
       </c>
       <c r="L25" s="15">
-        <v>-35.616438356164</v>
+        <v>-35.309278350515</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G26" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.076923076923</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J26" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K26" s="15">
         <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.172839506172</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.433734939759</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1434,14 +1434,14 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="14">
-        <v>1</v>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
@@ -1453,7 +1453,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
+        <v>7</v>
+      </c>
+      <c r="J15" s="14">
         <v>6</v>
       </c>
-      <c r="J15" s="14">
-        <v>5</v>
-      </c>
       <c r="K15" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N15" s="15">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F16" s="14">
+        <v>14</v>
+      </c>
+      <c r="G16" s="14">
+        <v>14</v>
+      </c>
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>13</v>
-      </c>
-      <c r="G16" s="14">
-        <v>18</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-27.777777777777</v>
-      </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.375</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.090909090909</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.060606060606</v>
+        <v>-55.405405405405</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.816753926701</v>
+        <v>-83.582089552238</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
-      </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
-      <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>5</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H17" s="15">
-        <v>77.777777777777</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J17" s="14">
         <v>32</v>
       </c>
       <c r="K17" s="15">
-        <v>37.5</v>
+        <v>59.375</v>
       </c>
       <c r="L17" s="15">
-        <v>10</v>
+        <v>27.5</v>
       </c>
       <c r="M17" s="15">
-        <v>46.666666666666</v>
+        <v>37.837837837837</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.987951807228</v>
+        <v>-42.045454545454</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,28 +1028,28 @@
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
         <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>72.222222222222</v>
+        <v>63.157894736842</v>
       </c>
       <c r="L18" s="15">
         <v>82.352941176470</v>
       </c>
       <c r="M18" s="15">
-        <v>-60.256410256410</v>
+        <v>-63.953488372093</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.091954022988</v>
+        <v>-92.191435768262</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.157894736842</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="I19" s="14">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J19" s="14">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.473684210526</v>
+        <v>-13.580246913580</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.136363636363</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.474820143884</v>
+        <v>-8.496732026143</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.095238095238</v>
+        <v>-38.325991189427</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.823529411764</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.390243902439</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>-44.642857142857</v>
+        <v>-45</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.370023419203</v>
+        <v>-96.432432432432</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
         <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>10.526315789473</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" s="17">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="J21" s="17">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.094890510948</v>
+        <v>0.682593856655</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.576323987538</v>
+        <v>-13.489736070381</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.540106951871</v>
+        <v>-28.915662650602</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.058823529411</v>
+        <v>-84.088457389428</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
         <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>-21.428571428571</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>12.5</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.333333333333</v>
+        <v>-8.411214953271</v>
       </c>
       <c r="I24" s="14">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="J24" s="14">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.299212598425</v>
+        <v>-8.212560386473</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.554603854389</v>
+        <v>-23.387096774193</v>
       </c>
       <c r="M24" s="15">
-        <v>33.208955223880</v>
+        <v>32.404181184669</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15">
-        <v>-15</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="F25" s="14">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G25" s="14">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.526315789473</v>
+        <v>-31.395348837209</v>
       </c>
       <c r="I25" s="14">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="J25" s="14">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="K25" s="15">
-        <v>-3.831417624521</v>
+        <v>-5.226480836236</v>
       </c>
       <c r="L25" s="15">
-        <v>-35.309278350515</v>
+        <v>-34.140435835351</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F26" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
-        <v>-41.666666666666</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I26" s="14">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J26" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.954545454545</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.896551724137</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -911,22 +911,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
         <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.714285714285</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.787234042553</v>
+        <v>-35.849056603773</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.405405405405</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.582089552238</v>
+        <v>-84.403669724770</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -977,38 +977,38 @@
       <c r="C17" s="14">
         <v>5</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="14">
+        <v>6</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
         <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>114.285714285714</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K17" s="15">
-        <v>59.375</v>
+        <v>47.368421052631</v>
       </c>
       <c r="L17" s="15">
-        <v>27.5</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>37.837837837837</v>
+        <v>43.589743589743</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.045454545454</v>
+        <v>-38.461538461538</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,17 +1018,17 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         <v>63.157894736842</v>
       </c>
       <c r="L18" s="15">
-        <v>82.352941176470</v>
+        <v>55</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.953488372093</v>
+        <v>-65.555555555555</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.191435768262</v>
+        <v>-92.705882352941</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.256410256410</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J19" s="14">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.580246913580</v>
+        <v>-16.477272727272</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.315789473684</v>
+        <v>-26.865671641791</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.496732026143</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.325991189427</v>
+        <v>-38.75</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I20" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.157894736842</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L20" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-45</v>
+        <v>-47.692307692307</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.432432432432</v>
+        <v>-96.516393442623</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>21.052631578947</v>
+        <v>-37.5</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H21" s="18">
-        <v>5</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I21" s="17">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="J21" s="17">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="K21" s="18">
-        <v>0.682593856655</v>
+        <v>-2.208201892744</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.489736070381</v>
+        <v>-17.553191489361</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.915662650602</v>
+        <v>-29.384965831435</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.088457389428</v>
+        <v>-84.239959328927</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>13</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>225</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M23" s="15">
         <v>-7.142857142857</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>-30.303030303030</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.411214953271</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="14">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="J24" s="14">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.212560386473</v>
+        <v>-9.706546275395</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.387096774193</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M24" s="15">
-        <v>32.404181184669</v>
+        <v>32.890365448505</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>-19.230769230769</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F25" s="14">
         <v>59</v>
       </c>
       <c r="G25" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.395348837209</v>
+        <v>-35.164835164835</v>
       </c>
       <c r="I25" s="14">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="J25" s="14">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.226480836236</v>
+        <v>-8.038585209003</v>
       </c>
       <c r="L25" s="15">
-        <v>-34.140435835351</v>
+        <v>-33.796296296296</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
         <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.695652173913</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I26" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J26" s="14">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K26" s="15">
-        <v>5.882352941176</v>
+        <v>8.988764044943</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.173913043478</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.255319148936</v>
+        <v>-9.345794392523</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-37.5</v>
+        <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-063pct.xlsx
+++ b/data/source/weekly/cs-en-us-063pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
+        <v>50</v>
+      </c>
+      <c r="I15" s="14">
+        <v>9</v>
+      </c>
+      <c r="J15" s="14">
+        <v>7</v>
+      </c>
+      <c r="K15" s="15">
+        <v>28.571428571428</v>
+      </c>
+      <c r="L15" s="15">
+        <v>200</v>
+      </c>
+      <c r="M15" s="15">
+        <v>80</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="I15" s="14">
-        <v>8</v>
-      </c>
-      <c r="J15" s="14">
-        <v>6</v>
-      </c>
-      <c r="K15" s="15">
-        <v>33.333333333333</v>
-      </c>
-      <c r="L15" s="15">
-        <v>166.666666666667</v>
-      </c>
-      <c r="M15" s="15">
-        <v>60</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-11.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-6.666666666666</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
         <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.526315789473</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.849056603773</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.410256410256</v>
+        <v>-56.626506024096</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.403669724770</v>
+        <v>-84.482758620689</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
         <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>25</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K17" s="15">
-        <v>47.368421052631</v>
+        <v>48.780487804878</v>
       </c>
       <c r="L17" s="15">
-        <v>16.666666666666</v>
+        <v>24.489795918367</v>
       </c>
       <c r="M17" s="15">
-        <v>43.589743589743</v>
+        <v>45.238095238095</v>
       </c>
       <c r="N17" s="15">
-        <v>-38.461538461538</v>
+        <v>-38.383838383838</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="14">
+      <c r="D18" s="14">
         <v>4</v>
       </c>
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I18" s="14">
         <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>63.157894736842</v>
+        <v>34.782608695652</v>
       </c>
       <c r="L18" s="15">
-        <v>55</v>
+        <v>40.909090909090</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.555555555555</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.705882352941</v>
+        <v>-93.246187363834</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="I19" s="14">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J19" s="14">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.477272727272</v>
+        <v>-16.931216931216</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.865671641791</v>
+        <v>-27.314814814814</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.259259259259</v>
+        <v>-8.187134502923</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.75</v>
+        <v>-37.944664031620</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>30</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
         <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.820512820512</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="M20" s="15">
-        <v>-47.692307692307</v>
+        <v>-46.268656716417</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.516393442623</v>
+        <v>-96.551724137931</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.896551724137</v>
+        <v>-9.638554216867</v>
       </c>
       <c r="I21" s="17">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="J21" s="17">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.208201892744</v>
+        <v>-2.366863905325</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.553191489361</v>
+        <v>-16.876574307304</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.384965831435</v>
+        <v>-28.416485900216</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.239959328927</v>
+        <v>-84.315589353612</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
         <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>116.666666666667</v>
+        <v>150</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.142857142857</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>-7.142857142857</v>
+        <v>7.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.586206896551</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G24" s="14">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15">
-        <v>-25</v>
+        <v>-14.545454545454</v>
       </c>
       <c r="I24" s="14">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="J24" s="14">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.706546275395</v>
+        <v>-9.421841541755</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.076923076923</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>32.890365448505</v>
+        <v>32.601880877742</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-41.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G25" s="14">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.164835164835</v>
+        <v>-17.045454545454</v>
       </c>
       <c r="I25" s="14">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="J25" s="14">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.038585209003</v>
+        <v>-6.686930091185</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.796296296296</v>
+        <v>-31.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
         <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>19.047619047619</v>
+        <v>58.823529411764</v>
       </c>
       <c r="I26" s="14">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J26" s="14">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K26" s="15">
-        <v>8.988764044943</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.345794392523</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1453,7 +1453,7 @@
         <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>100</v>
       </c>
       <c r="L31" s="15">
         <v>-33.333333333333</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
